--- a/artfynd/Floarna artfynd.xlsx
+++ b/artfynd/Floarna artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9946,57 +9946,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>26902775</v>
+        <v>134969621</v>
       </c>
       <c r="B86" t="n">
-        <v>57602</v>
+        <v>79130</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100063</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stenbittjärnen, s:a Haverö, Mpd</t>
+          <t>Rörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>502888</v>
+        <v>502963</v>
       </c>
       <c r="R86" t="n">
-        <v>6906660</v>
+        <v>6905609</v>
       </c>
       <c r="S86" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10020,27 +10011,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2007-07-15</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2007-07-15</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Låg på en tuva men inga tecken på lyckad häckning.</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10055,74 +10031,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Björn Svensson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Björn Svensson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>24068832</v>
+        <v>134961773</v>
       </c>
       <c r="B87" t="n">
-        <v>57132</v>
+        <v>79992</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stenbittjärnen, s:a Haverö, Mpd</t>
+          <t>Rörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>502888</v>
+        <v>502929</v>
       </c>
       <c r="R87" t="n">
-        <v>6906660</v>
+        <v>6905630</v>
       </c>
       <c r="S87" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10146,22 +10108,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2006-08-16</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2006-08-16</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10176,57 +10128,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lars Berggren</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lars Berggren, Carl-Fredrik  Yri</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>96790544</v>
+        <v>134965706</v>
       </c>
       <c r="B88" t="n">
-        <v>92183</v>
+        <v>79992</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Rörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>502436</v>
+        <v>502961</v>
       </c>
       <c r="R88" t="n">
-        <v>6907171</v>
+        <v>6905602</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10253,12 +10205,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10269,43 +10221,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
-        </is>
-      </c>
-      <c r="AN88" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>2 substratenheter # gammal tallåga av fallen klen torraka, bakom block och sedan länge fallen torrtall av lite sämre kvalitet</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>96790546</v>
+        <v>134960891</v>
       </c>
       <c r="B89" t="n">
-        <v>78993</v>
+        <v>80488</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10313,34 +10248,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Rörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>502370</v>
+        <v>502937</v>
       </c>
       <c r="R89" t="n">
-        <v>6907089</v>
+        <v>6905655</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10367,12 +10302,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10383,78 +10318,61 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>tallnaturskog med gamla tallöverståndare på blockig mark, ovan sumpskogsparti</t>
-        </is>
-      </c>
-      <c r="AN89" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>2 substratenheter # fallna gamla torrakor</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>96790548</v>
+        <v>134964850</v>
       </c>
       <c r="B90" t="n">
-        <v>78993</v>
+        <v>100220</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>222467</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Rörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>502361</v>
+        <v>502944</v>
       </c>
       <c r="R90" t="n">
-        <v>6907122</v>
+        <v>6905640</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10481,12 +10399,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10497,82 +10415,64 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>ogallrad 130-årig lingontallskog med gamla tallöverståndare på blockig mark</t>
-        </is>
-      </c>
-      <c r="AN90" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>2 substratenheter # fallna gamla torrakor</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>111804077</v>
+        <v>134964147</v>
       </c>
       <c r="B91" t="n">
-        <v>93213</v>
+        <v>79131</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Torrflonäsberget, Mpd</t>
+          <t>Rörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>502370</v>
+        <v>502964</v>
       </c>
       <c r="R91" t="n">
-        <v>6906961</v>
+        <v>6905613</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10596,22 +10496,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10626,60 +10516,69 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>96790545</v>
+        <v>26902775</v>
       </c>
       <c r="B92" t="n">
-        <v>91962</v>
+        <v>57602</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2079</v>
+        <v>100063</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Stenbittjärnen, s:a Haverö, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>502430</v>
+        <v>502888</v>
       </c>
       <c r="R92" t="n">
-        <v>6907162</v>
+        <v>6906660</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10703,12 +10602,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2007-07-15</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2007-07-15</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Låg på en tuva men inga tecken på lyckad häckning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10719,81 +10633,78 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
-        </is>
-      </c>
-      <c r="AN92" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Björn Svensson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Björn Svensson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>96790514</v>
+        <v>24068832</v>
       </c>
       <c r="B93" t="n">
-        <v>78993</v>
+        <v>57132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Stenbittjärnen, s:a Haverö, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>502414</v>
+        <v>502888</v>
       </c>
       <c r="R93" t="n">
-        <v>6907420</v>
+        <v>6906660</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10817,12 +10728,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2006-08-16</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2006-08-16</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10833,78 +10754,61 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>tallnaturskog i blockig östsluttning</t>
-        </is>
-      </c>
-      <c r="AN93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>1 substratenheter # fallen torraka</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Lars Berggren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Lars Berggren, Carl-Fredrik  Yri</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>96790512</v>
+        <v>96790544</v>
       </c>
       <c r="B94" t="n">
-        <v>81312</v>
+        <v>92183</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1049</v>
+        <v>65</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>502354</v>
+        <v>502436</v>
       </c>
       <c r="R94" t="n">
-        <v>6907377</v>
+        <v>6907171</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10931,12 +10835,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10950,15 +10854,15 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>tallnaturskog på blockig mark</t>
+          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>1 substratenheter # torraka</t>
+          <t>2 substratenheter # gammal tallåga av fallen klen torraka, bakom block och sedan länge fallen torrtall av lite sämre kvalitet</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10980,10 +10884,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>96790515</v>
+        <v>96790546</v>
       </c>
       <c r="B95" t="n">
-        <v>80432</v>
+        <v>78993</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10991,34 +10895,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502410</v>
+        <v>502370</v>
       </c>
       <c r="R95" t="n">
-        <v>6907490</v>
+        <v>6907089</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11045,12 +10949,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11064,15 +10968,15 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>tallnaturskog i blockig östsluttning</t>
+          <t>tallnaturskog med gamla tallöverståndare på blockig mark, ovan sumpskogsparti</t>
         </is>
       </c>
       <c r="AN95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal krumböjd björk</t>
+          <t>2 substratenheter # fallna gamla torrakor</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11094,10 +10998,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>96790513</v>
+        <v>96790548</v>
       </c>
       <c r="B96" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11105,34 +11009,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502433</v>
+        <v>502361</v>
       </c>
       <c r="R96" t="n">
-        <v>6907292</v>
+        <v>6907122</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11159,12 +11063,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11178,15 +11082,15 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>tallnaturskog i blockig östsluttning</t>
+          <t>ogallrad 130-årig lingontallskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>5 substratenheter # grova brandhögstubbar</t>
+          <t>2 substratenheter # fallna gamla torrakor</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11208,48 +11112,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96790535</v>
+        <v>111804077</v>
       </c>
       <c r="B97" t="n">
-        <v>78993</v>
+        <v>93213</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Torrflonäsberget, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>502412</v>
+        <v>502370</v>
       </c>
       <c r="R97" t="n">
-        <v>6907750</v>
+        <v>6906961</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11273,12 +11178,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11289,43 +11204,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>120-årig blockig tallskog nära sjön</t>
-        </is>
-      </c>
-      <c r="AN97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>1 substratenheter # fallen grov gammal torraka</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>96790533</v>
+        <v>96790545</v>
       </c>
       <c r="B98" t="n">
-        <v>89156</v>
+        <v>91962</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11333,43 +11231,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4412</v>
+        <v>2079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>502373</v>
+        <v>502430</v>
       </c>
       <c r="R98" t="n">
-        <v>6907809</v>
+        <v>6907162</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11396,12 +11285,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11415,7 +11304,15 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>140-årig blockig tallskog, med granunderväxt och spridda aspar</t>
+          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
+        </is>
+      </c>
+      <c r="AN98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11437,10 +11334,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>96790532</v>
+        <v>96790514</v>
       </c>
       <c r="B99" t="n">
-        <v>80432</v>
+        <v>78993</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11448,34 +11345,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>502362</v>
+        <v>502414</v>
       </c>
       <c r="R99" t="n">
-        <v>6907811</v>
+        <v>6907420</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11521,7 +11418,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>140-årig barrblandskog med gott om asp</t>
+          <t>tallnaturskog i blockig östsluttning</t>
         </is>
       </c>
       <c r="AN99" t="n">
@@ -11529,7 +11426,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal asp</t>
+          <t>1 substratenheter # fallen torraka</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11551,10 +11448,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>96790534</v>
+        <v>96790512</v>
       </c>
       <c r="B100" t="n">
-        <v>79085</v>
+        <v>81312</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11562,34 +11459,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>502402</v>
+        <v>502354</v>
       </c>
       <c r="R100" t="n">
-        <v>6907740</v>
+        <v>6907377</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11635,7 +11532,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>120-årig blockig tallskog, i kant mot sump</t>
+          <t>tallnaturskog på blockig mark</t>
         </is>
       </c>
       <c r="AN100" t="n">
@@ -11643,7 +11540,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>1 substratenheter # torraka</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11662,6 +11559,3989 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>96790515</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lokberget, öst om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>502410</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6907490</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>tallnaturskog i blockig östsluttning</t>
+        </is>
+      </c>
+      <c r="AN101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal krumböjd björk</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>96790513</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Lokberget, nordväst om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>502433</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6907292</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>tallnaturskog i blockig östsluttning</t>
+        </is>
+      </c>
+      <c r="AN102" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>5 substratenheter # grova brandhögstubbar</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>96790535</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78993</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>353</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lokberget, öst om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>502412</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6907750</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>120-årig blockig tallskog nära sjön</t>
+        </is>
+      </c>
+      <c r="AN103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>1 substratenheter # fallen grov gammal torraka</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>96790533</v>
+      </c>
+      <c r="B104" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lokberget, öst om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>502373</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6907809</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>140-årig blockig tallskog, med granunderväxt och spridda aspar</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>96790532</v>
+      </c>
+      <c r="B105" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lokberget, öst om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>502362</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6907811</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>140-årig barrblandskog med gott om asp</t>
+        </is>
+      </c>
+      <c r="AN105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal asp</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>96790534</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lokberget, öst om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>502402</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6907740</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>120-årig blockig tallskog, i kant mot sump</t>
+        </is>
+      </c>
+      <c r="AN106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov brandhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>134958086</v>
+      </c>
+      <c r="B107" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>503072</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6905853</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>134970483</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>503042</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6905794</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>134966338</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>503042</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6905796</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>134968660</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>353</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>503205</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6906127</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>134958497</v>
+      </c>
+      <c r="B111" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>503146</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6906009</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>134960676</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>503129</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6905997</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>134966756</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>503131</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6906076</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>134970054</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>503060</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6905865</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>134963939</v>
+      </c>
+      <c r="B115" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>503142</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6906039</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>134961562</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>503195</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6906171</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>134961997</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>503137</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6906035</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>134964561</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>503215</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6906123</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>134966337</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>503139</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6906002</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>134970053</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>503193</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6906126</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>134968039</v>
+      </c>
+      <c r="B121" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>503172</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6906090</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>134968447</v>
+      </c>
+      <c r="B122" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>503142</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6906039</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>134968867</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>503193</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6906172</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>134956702</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>503142</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6906041</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>134958500</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>503137</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6906035</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>134958720</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>503111</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6906007</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>134962693</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>503216</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6906119</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>134967387</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>503196</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6906173</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>134968866</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>503171</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6906073</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>134955926</v>
+      </c>
+      <c r="B130" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>503131</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6906105</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>134967185</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>503191</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6906087</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>134967807</v>
+      </c>
+      <c r="B132" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>503139</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6906009</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>134968042</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>503120</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6906078</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>134970482</v>
+      </c>
+      <c r="B134" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>503143</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6906039</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134959129</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>353</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>503123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6906347</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134967808</v>
+      </c>
+      <c r="B136" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>503116</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6906339</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>134959531</v>
+      </c>
+      <c r="B137" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>503138</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6906322</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>134963938</v>
+      </c>
+      <c r="B138" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>503145</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6906340</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>134965491</v>
+      </c>
+      <c r="B139" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>503137</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6906324</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>134960890</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>503156</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6906351</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Floarna artfynd.xlsx
+++ b/artfynd/Floarna artfynd.xlsx
@@ -1643,59 +1643,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96661661</v>
+        <v>96790491</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501308</v>
+        <v>501592</v>
       </c>
       <c r="R11" t="n">
-        <v>6907628</v>
+        <v>6907850</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,12 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,26 +1724,43 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, på blockig höjd</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # fallen grov brandhögstubbe</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96790491</v>
+        <v>96790497</v>
       </c>
       <c r="B12" t="n">
-        <v>78993</v>
+        <v>81312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,21 +1768,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501592</v>
+        <v>501499</v>
       </c>
       <c r="R12" t="n">
-        <v>6907850</v>
+        <v>6907916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1841,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, på blockig höjd</t>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -1843,7 +1849,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # fallen grov brandhögstubbe</t>
+          <t>1 substratenheter # grov gammal torraka</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1865,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96790492</v>
+        <v>96790498</v>
       </c>
       <c r="B13" t="n">
-        <v>78993</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501507</v>
+        <v>501504</v>
       </c>
       <c r="R13" t="n">
-        <v>6907968</v>
+        <v>6907945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1963,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # fallen torraka</t>
+          <t>1 substratenheter # gammal björk</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1979,48 +1985,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96790501</v>
+        <v>96661273</v>
       </c>
       <c r="B14" t="n">
-        <v>78993</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501534</v>
+        <v>501303</v>
       </c>
       <c r="R14" t="n">
-        <v>6907977</v>
+        <v>6907799</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,12 +2061,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,81 +2077,75 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallnaturskog i blockig nordvästsida</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>1 substratenheter # fallen torraka</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96790499</v>
+        <v>96661387</v>
       </c>
       <c r="B15" t="n">
-        <v>80298</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501524</v>
+        <v>501301</v>
       </c>
       <c r="R15" t="n">
-        <v>6907968</v>
+        <v>6907699</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2158,12 +2169,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,81 +2185,75 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallnaturskog i blockig nordvästsida</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # 140-årig asp</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96790497</v>
+        <v>96661586</v>
       </c>
       <c r="B16" t="n">
-        <v>81312</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501499</v>
+        <v>501349</v>
       </c>
       <c r="R16" t="n">
-        <v>6907916</v>
+        <v>6907708</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,12 +2277,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,43 +2293,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
-        </is>
-      </c>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal torraka</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96790493</v>
+        <v>96661661</v>
       </c>
       <c r="B17" t="n">
-        <v>92083</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,37 +2320,48 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501591</v>
+        <v>501308</v>
       </c>
       <c r="R17" t="n">
-        <v>6908025</v>
+        <v>6907628</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2386,12 +2385,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,81 +2401,75 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
-        </is>
-      </c>
-      <c r="AN17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga liggande på block</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96790500</v>
+        <v>96662350</v>
       </c>
       <c r="B18" t="n">
-        <v>91831</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501534</v>
+        <v>501130</v>
       </c>
       <c r="R18" t="n">
-        <v>6907977</v>
+        <v>6907720</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,12 +2493,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,81 +2509,75 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallnaturskog i blockig nordvästsida</t>
-        </is>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under fallen hård torraka</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96790498</v>
+        <v>96662466</v>
       </c>
       <c r="B19" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501504</v>
+        <v>501098</v>
       </c>
       <c r="R19" t="n">
-        <v>6907945</v>
+        <v>6907809</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2614,12 +2601,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,40 +2617,23 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal björk</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96660901</v>
+        <v>99045822</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2693,29 +2663,30 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Loktjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501354</v>
+        <v>501303</v>
       </c>
       <c r="R20" t="n">
-        <v>6908015</v>
+        <v>6907798</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,6 +2708,11 @@
           <t>Haverö</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Y-Ång-0125</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
           <t>2021-10-15</t>
@@ -2747,14 +2723,25 @@
           <t>2021-10-15</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Många dellokaler inom området</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2767,63 +2754,56 @@
           <t>Agneta Toomingas</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96661273</v>
+        <v>96790494</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501303</v>
+        <v>501519</v>
       </c>
       <c r="R21" t="n">
-        <v>6907799</v>
+        <v>6907920</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2847,12 +2827,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,75 +2843,78 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>grov gammal torraka och brandhögstubbar</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96661387</v>
+        <v>96790496</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>79917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501301</v>
+        <v>501499</v>
       </c>
       <c r="R22" t="n">
-        <v>6907699</v>
+        <v>6907916</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2955,12 +2938,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2971,75 +2954,81 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>2 substratenheter # grova gamla torrakor</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96661586</v>
+        <v>96790492</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>78993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501349</v>
+        <v>501507</v>
       </c>
       <c r="R23" t="n">
-        <v>6907708</v>
+        <v>6907968</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3063,12 +3052,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,75 +3068,81 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>1 substratenheter # fallen torraka</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96662350</v>
+        <v>96790501</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>78993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501130</v>
+        <v>501534</v>
       </c>
       <c r="R24" t="n">
-        <v>6907720</v>
+        <v>6907977</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3171,12 +3166,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,75 +3182,81 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog i blockig nordvästsida</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>1 substratenheter # fallen torraka</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96662466</v>
+        <v>96790499</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>80298</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>501098</v>
+        <v>501524</v>
       </c>
       <c r="R25" t="n">
-        <v>6907809</v>
+        <v>6907968</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3279,12 +3280,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3295,26 +3296,43 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog i blockig nordvästsida</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # 140-årig asp</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96663511</v>
+        <v>96790493</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>92083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,48 +3340,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501174</v>
+        <v>501591</v>
       </c>
       <c r="R26" t="n">
-        <v>6908019</v>
+        <v>6908025</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3387,12 +3394,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,76 +3410,81 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga liggande på block</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>99045822</v>
+        <v>96790500</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>91831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Loktjärnarna, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501303</v>
+        <v>501534</v>
       </c>
       <c r="R27" t="n">
-        <v>6907798</v>
+        <v>6907977</v>
       </c>
       <c r="S27" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3494,24 +3506,14 @@
           <t>Haverö</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Y-Ång-0125</t>
-        </is>
-      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Många dellokaler inom området</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3520,38 +3522,45 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>140-årig, senvuxen tallnaturskog i blockig nordvästsida</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under fallen hård torraka</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96790494</v>
+        <v>96790502</v>
       </c>
       <c r="B28" t="n">
-        <v>79085</v>
+        <v>5495</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,21 +3568,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3583,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501519</v>
+        <v>501644</v>
       </c>
       <c r="R28" t="n">
-        <v>6907920</v>
+        <v>6908110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3632,12 +3641,15 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
-        </is>
+          <t>140-årig, senvuxen tallskog i blockig nordsida</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>grov gammal torraka och brandhögstubbar</t>
+          <t>1 substratenheter # typiska spår i gammal tall</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3659,10 +3671,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96790496</v>
+        <v>126305538</v>
       </c>
       <c r="B29" t="n">
-        <v>79917</v>
+        <v>5495</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3670,37 +3682,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Norr Loktjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501499</v>
+        <v>501557</v>
       </c>
       <c r="R29" t="n">
-        <v>6907916</v>
+        <v>6908103</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3724,12 +3745,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,83 +3759,78 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig nordvästsida</t>
-        </is>
-      </c>
-      <c r="AN29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>2 substratenheter # grova gamla torrakor</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96790502</v>
+        <v>96660901</v>
       </c>
       <c r="B30" t="n">
-        <v>5495</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>501644</v>
+        <v>501354</v>
       </c>
       <c r="R30" t="n">
-        <v>6908110</v>
+        <v>6908015</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3838,12 +3854,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3854,87 +3870,72 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>140-årig, senvuxen tallskog i blockig nordsida</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>1 substratenheter # typiska spår i gammal tall</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126305538</v>
+        <v>96663511</v>
       </c>
       <c r="B31" t="n">
-        <v>5495</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norr Loktjärnarna, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501557</v>
+        <v>501174</v>
       </c>
       <c r="R31" t="n">
-        <v>6908103</v>
+        <v>6908019</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3961,12 +3962,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,19 +3976,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>96790551</v>
+        <v>96790536</v>
       </c>
       <c r="B47" t="n">
         <v>78993</v>
@@ -5568,14 +5568,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Lokberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502218</v>
+        <v>502010</v>
       </c>
       <c r="R47" t="n">
-        <v>6907127</v>
+        <v>6907394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>ogallrad 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
+          <t>tallnaturskog i blockig nordsida med gammeltallar</t>
         </is>
       </c>
       <c r="AN47" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga upphängd mot stenblock</t>
+          <t>1 substratenheter # fallen gammal torraka</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96790552</v>
+        <v>96790539</v>
       </c>
       <c r="B48" t="n">
         <v>78993</v>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502176</v>
+        <v>502315</v>
       </c>
       <c r="R48" t="n">
-        <v>6907106</v>
+        <v>6907395</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>ogallrad 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
+          <t>140-årig tallnaturskog med enstaka gamla tallöverståndare, men fler gamla björkar, på blockig mark</t>
         </is>
       </c>
       <c r="AN48" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga</t>
+          <t>1 substratenheter # fallen lång och grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5765,48 +5765,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133848547</v>
+        <v>96790540</v>
       </c>
       <c r="B49" t="n">
-        <v>92546</v>
+        <v>78993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lokberget, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>501845</v>
+        <v>502340</v>
       </c>
       <c r="R49" t="n">
-        <v>6907159</v>
+        <v>6907314</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5846,52 +5846,65 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>tallnaturskog med enstaka gamla tallöverståndare på blockig mark</t>
+        </is>
+      </c>
+      <c r="AN49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>1 substratenheter # lutande gammal torrak, lutar ca 30 grader, på ovansidan</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering Y-län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96790554</v>
+        <v>96790551</v>
       </c>
       <c r="B50" t="n">
-        <v>92083</v>
+        <v>78993</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5901,10 +5914,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502210</v>
+        <v>502218</v>
       </c>
       <c r="R50" t="n">
-        <v>6907045</v>
+        <v>6907127</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5958,7 +5971,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>1 substratenheter # rest av äldre tallåga</t>
+          <t>1 substratenheter # gammal tallåga upphängd mot stenblock</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5980,10 +5993,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96790543</v>
+        <v>96790552</v>
       </c>
       <c r="B51" t="n">
-        <v>93197</v>
+        <v>78993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5991,21 +6004,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6015,10 +6028,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502323</v>
+        <v>502176</v>
       </c>
       <c r="R51" t="n">
-        <v>6907190</v>
+        <v>6907106</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6064,12 +6077,15 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
-        </is>
+          <t>ogallrad 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
+        </is>
+      </c>
+      <c r="AN51" t="n">
+        <v>1</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>spridd i beståndet på mager mark</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6091,52 +6107,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>53489721</v>
+        <v>133848547</v>
       </c>
       <c r="B52" t="n">
-        <v>80432</v>
+        <v>92546</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lokberget, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>501803</v>
+        <v>501845</v>
       </c>
       <c r="R52" t="n">
-        <v>6907199</v>
+        <v>6907159</v>
       </c>
       <c r="S52" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6160,12 +6172,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>1997-09-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>1997-09-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6176,57 +6188,52 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>SCA Skogsmark</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>96790547</v>
+        <v>96790554</v>
       </c>
       <c r="B53" t="n">
-        <v>80432</v>
+        <v>92083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6236,10 +6243,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>502320</v>
+        <v>502210</v>
       </c>
       <c r="R53" t="n">
-        <v>6907040</v>
+        <v>6907045</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6285,15 +6292,15 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>kant mellan tallnaturskog och grannaturskog i kärrkant</t>
+          <t>ogallrad 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>5 substratenheter # gamla sälgar</t>
+          <t>1 substratenheter # rest av äldre tallåga</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6315,10 +6322,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>96790553</v>
+        <v>96790543</v>
       </c>
       <c r="B54" t="n">
-        <v>5495</v>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6326,21 +6333,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6350,10 +6357,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>502190</v>
+        <v>502323</v>
       </c>
       <c r="R54" t="n">
-        <v>6907076</v>
+        <v>6907190</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6399,15 +6406,12 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>halvljus 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
-        </is>
-      </c>
-      <c r="AN54" t="n">
-        <v>2</v>
+          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
+        </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>2 substratenheter # typiska spår i gamla tallar</t>
+          <t>spridd i beståndet på mager mark</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6429,10 +6433,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>96790550</v>
+        <v>53489721</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6440,37 +6444,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Lokberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>502237</v>
+        <v>501803</v>
       </c>
       <c r="R55" t="n">
-        <v>6907134</v>
+        <v>6907199</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6494,12 +6502,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>1997-09-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>1997-09-17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,26 +6521,18 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>ojämn 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
-        </is>
-      </c>
-      <c r="AN55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>4 substratenheter # brandhögstubbar</t>
+          <t>SCA Skogsmark</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Tomas Rydkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6543,10 +6543,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>96790549</v>
+        <v>96790547</v>
       </c>
       <c r="B56" t="n">
-        <v>79917</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6554,21 +6554,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502224</v>
+        <v>502320</v>
       </c>
       <c r="R56" t="n">
-        <v>6907150</v>
+        <v>6907040</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6627,15 +6627,15 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>ojämn 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
+          <t>kant mellan tallnaturskog och grannaturskog i kärrkant</t>
         </is>
       </c>
       <c r="AN56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och hög skorstenshögstubbe</t>
+          <t>5 substratenheter # gamla sälgar</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6657,45 +6657,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>96790510</v>
+        <v>96790541</v>
       </c>
       <c r="B57" t="n">
-        <v>92198</v>
+        <v>5495</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>71</v>
+        <v>101410</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502333</v>
+        <v>502147</v>
       </c>
       <c r="R57" t="n">
-        <v>6907630</v>
+        <v>6907364</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6722,12 +6722,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>tallnaturskog med gamla modertallar på blockig mark</t>
+          <t>halvljus 130-årig tallnaturskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN57" t="n">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>1 substratenheter # sedan länge fallen torraka med brandspår, fjolårsfruktkropp</t>
+          <t>1 substratenheter # typiska spår i gammal tall</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6771,10 +6771,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96790536</v>
+        <v>96790553</v>
       </c>
       <c r="B58" t="n">
-        <v>78993</v>
+        <v>5495</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6782,34 +6782,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lokberget, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502010</v>
+        <v>502190</v>
       </c>
       <c r="R58" t="n">
-        <v>6907394</v>
+        <v>6907076</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6855,15 +6855,15 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>tallnaturskog i blockig nordsida med gammeltallar</t>
+          <t>halvljus 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>1 substratenheter # fallen gammal torraka</t>
+          <t>2 substratenheter # typiska spår i gamla tallar</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6885,10 +6885,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>96790539</v>
+        <v>96790550</v>
       </c>
       <c r="B59" t="n">
-        <v>78993</v>
+        <v>79085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6896,21 +6896,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6920,10 +6920,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502315</v>
+        <v>502237</v>
       </c>
       <c r="R59" t="n">
-        <v>6907395</v>
+        <v>6907134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6969,15 +6969,15 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog med enstaka gamla tallöverståndare, men fler gamla björkar, på blockig mark</t>
+          <t>ojämn 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>1 substratenheter # fallen lång och grov skorstenshögstubbe</t>
+          <t>4 substratenheter # brandhögstubbar</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>96790540</v>
+        <v>96790542</v>
       </c>
       <c r="B60" t="n">
-        <v>78993</v>
+        <v>79917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7010,21 +7010,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502340</v>
+        <v>502258</v>
       </c>
       <c r="R60" t="n">
-        <v>6907314</v>
+        <v>6907221</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>tallnaturskog med enstaka gamla tallöverståndare på blockig mark</t>
+          <t>120-årig, ogallrad blåbärstallskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN60" t="n">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>1 substratenheter # lutande gammal torrak, lutar ca 30 grader, på ovansidan</t>
+          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>96790538</v>
+        <v>96790549</v>
       </c>
       <c r="B61" t="n">
-        <v>80298</v>
+        <v>79917</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7124,34 +7124,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>388</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lokberget, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502239</v>
+        <v>502224</v>
       </c>
       <c r="R61" t="n">
-        <v>6907503</v>
+        <v>6907150</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>olikåldrig naturskogsartad blåbärsbarrskog</t>
+          <t>ojämn 130-årig blåbärstallskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN61" t="n">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre asp med stamskada</t>
+          <t>1 substratenheter # grov och hög skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7227,32 +7227,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>96790511</v>
+        <v>96790510</v>
       </c>
       <c r="B62" t="n">
-        <v>91831</v>
+        <v>92198</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3242</v>
+        <v>71</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502325</v>
+        <v>502333</v>
       </c>
       <c r="R62" t="n">
-        <v>6907524</v>
+        <v>6907630</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>tallnaturskog på blockig mark</t>
+          <t>tallnaturskog med gamla modertallar på blockig mark</t>
         </is>
       </c>
       <c r="AN62" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>1 substratenheter # sedan länge fallen torraka med brandspår, upphängd, på hård ved under</t>
+          <t>1 substratenheter # sedan länge fallen torraka med brandspår, fjolårsfruktkropp</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96790537</v>
+        <v>96790538</v>
       </c>
       <c r="B63" t="n">
-        <v>91930</v>
+        <v>80298</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>388</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502228</v>
+        <v>502239</v>
       </c>
       <c r="R63" t="n">
         <v>6907503</v>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tall</t>
+          <t>1 substratenheter # äldre asp med stamskada</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7455,45 +7455,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>96790541</v>
+        <v>96790490</v>
       </c>
       <c r="B64" t="n">
-        <v>5495</v>
+        <v>91394</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>101410</v>
+        <v>2051</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502147</v>
+        <v>501712</v>
       </c>
       <c r="R64" t="n">
-        <v>6907364</v>
+        <v>6907949</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7520,12 +7529,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7539,15 +7548,12 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>halvljus 130-årig tallnaturskog med gamla tallöverståndare på blockig mark</t>
-        </is>
-      </c>
-      <c r="AN64" t="n">
-        <v>1</v>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, på blockig höjd</t>
+        </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>1 substratenheter # typiska spår i gammal tall</t>
+          <t>bland lingon, lav och väggmossa, med 15 cm lång fot</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7569,10 +7575,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>96790542</v>
+        <v>96790511</v>
       </c>
       <c r="B65" t="n">
-        <v>79917</v>
+        <v>91831</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7580,34 +7586,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>3242</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>502258</v>
+        <v>502325</v>
       </c>
       <c r="R65" t="n">
-        <v>6907221</v>
+        <v>6907524</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7634,12 +7640,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7653,7 +7659,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>120-årig, ogallrad blåbärstallskog med gamla tallöverståndare på blockig mark</t>
+          <t>tallnaturskog på blockig mark</t>
         </is>
       </c>
       <c r="AN65" t="n">
@@ -7661,7 +7667,7 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov skorstenshögstubbe</t>
+          <t>1 substratenheter # sedan länge fallen torraka med brandspår, upphängd, på hård ved under</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7683,10 +7689,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>96790519</v>
+        <v>96790531</v>
       </c>
       <c r="B66" t="n">
-        <v>97358</v>
+        <v>89156</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7694,34 +7700,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>4412</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502153</v>
+        <v>502314</v>
       </c>
       <c r="R66" t="n">
-        <v>6908085</v>
+        <v>6907960</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7767,15 +7782,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>140-årig mossig blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>1 substratenheter # äldre tallåga</t>
+          <t>140-årig blåbärstallskog, med lite granunderväxt</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7797,10 +7804,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96790525</v>
+        <v>96790537</v>
       </c>
       <c r="B67" t="n">
-        <v>97358</v>
+        <v>91930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7808,34 +7815,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>502302</v>
+        <v>502228</v>
       </c>
       <c r="R67" t="n">
-        <v>6908010</v>
+        <v>6907503</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7862,12 +7869,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7881,7 +7888,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>140-årig barrblandskog i terrängsvacka</t>
+          <t>olikåldrig naturskogsartad blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AN67" t="n">
@@ -7889,7 +7896,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre tallåga</t>
+          <t>1 substratenheter # gammal tall</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7911,32 +7918,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96790489</v>
+        <v>96790508</v>
       </c>
       <c r="B68" t="n">
-        <v>78993</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7946,10 +7953,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>501804</v>
+        <v>502276</v>
       </c>
       <c r="R68" t="n">
-        <v>6907988</v>
+        <v>6907827</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7995,15 +8002,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig västsida</t>
-        </is>
-      </c>
-      <c r="AN68" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>4 substratenheter # gamla hårda torrakor, liggande mot block</t>
+          <t>naturskogsartad tallskog i blockig östsluttning</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8025,10 +8024,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96790529</v>
+        <v>96790519</v>
       </c>
       <c r="B69" t="n">
-        <v>80298</v>
+        <v>97358</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8036,21 +8035,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>388</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8060,10 +8059,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>502292</v>
+        <v>502153</v>
       </c>
       <c r="R69" t="n">
-        <v>6907991</v>
+        <v>6908085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8109,15 +8108,15 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>140-årig tallskog med gott om asp</t>
+          <t>140-årig mossig blåbärsgranskog</t>
         </is>
       </c>
       <c r="AN69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>2 substratenheter # gammal asp och asphögstubbe</t>
+          <t>1 substratenheter # äldre tallåga</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8139,54 +8138,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>96790490</v>
+        <v>96790525</v>
       </c>
       <c r="B70" t="n">
-        <v>91394</v>
+        <v>97358</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2051</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>501712</v>
+        <v>502302</v>
       </c>
       <c r="R70" t="n">
-        <v>6907949</v>
+        <v>6908010</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8232,12 +8222,15 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>140-årig, senvuxen tallnaturskog med gamla tallar, på blockig höjd</t>
-        </is>
+          <t>140-årig barrblandskog i terrängsvacka</t>
+        </is>
+      </c>
+      <c r="AN70" t="n">
+        <v>1</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>bland lingon, lav och väggmossa, med 15 cm lång fot</t>
+          <t>1 substratenheter # äldre tallåga</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8259,45 +8252,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96790517</v>
+        <v>96790489</v>
       </c>
       <c r="B71" t="n">
-        <v>92632</v>
+        <v>78993</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502213</v>
+        <v>501804</v>
       </c>
       <c r="R71" t="n">
-        <v>6908014</v>
+        <v>6907988</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8343,15 +8336,15 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>150-årig barrblandskog med lågörtsfläckat och asp</t>
+          <t>140-årig, senvuxen tallnaturskog med gamla tallar, i blockig västsida</t>
         </is>
       </c>
       <c r="AN71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov torrgran</t>
+          <t>4 substratenheter # gamla hårda torrakor, liggande mot block</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8373,10 +8366,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96790524</v>
+        <v>96790529</v>
       </c>
       <c r="B72" t="n">
-        <v>89156</v>
+        <v>80298</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8384,43 +8377,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4412</v>
+        <v>388</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502246</v>
+        <v>502292</v>
       </c>
       <c r="R72" t="n">
-        <v>6908012</v>
+        <v>6907991</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8466,7 +8450,15 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>140-årig blåbärstallskog, med lite granunderväxt</t>
+          <t>140-årig tallskog med gott om asp</t>
+        </is>
+      </c>
+      <c r="AN72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>2 substratenheter # gammal asp och asphögstubbe</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8488,54 +8480,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>96790531</v>
+        <v>96790517</v>
       </c>
       <c r="B73" t="n">
-        <v>89156</v>
+        <v>92632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4412</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502314</v>
+        <v>502213</v>
       </c>
       <c r="R73" t="n">
-        <v>6907960</v>
+        <v>6908014</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8581,7 +8564,15 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>140-årig blåbärstallskog, med lite granunderväxt</t>
+          <t>150-årig barrblandskog med lågörtsfläckat och asp</t>
+        </is>
+      </c>
+      <c r="AN73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov torrgran</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8603,10 +8594,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96790518</v>
+        <v>96790488</v>
       </c>
       <c r="B74" t="n">
-        <v>80432</v>
+        <v>93189</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8614,34 +8605,43 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502167</v>
+        <v>501832</v>
       </c>
       <c r="R74" t="n">
-        <v>6908081</v>
+        <v>6908125</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8687,15 +8687,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>140-årig mossig blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AN74" t="n">
-        <v>1</v>
+          <t>140-årig, senvuxen tallskog</t>
+        </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre klen sälg</t>
+          <t>i stigkant</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8717,10 +8714,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>96790521</v>
+        <v>96790522</v>
       </c>
       <c r="B75" t="n">
-        <v>80432</v>
+        <v>89156</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8728,34 +8725,43 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>502153</v>
+        <v>502167</v>
       </c>
       <c r="R75" t="n">
-        <v>6908101</v>
+        <v>6908110</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8802,14 +8808,6 @@
       <c r="AI75" t="inlineStr">
         <is>
           <t>140-årig blåbärstallskog, med graninslag</t>
-        </is>
-      </c>
-      <c r="AN75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>1 substratenheter # äldre klen sälg</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8831,45 +8829,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>96790508</v>
+        <v>96790524</v>
       </c>
       <c r="B76" t="n">
-        <v>99118</v>
+        <v>89156</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>502276</v>
+        <v>502246</v>
       </c>
       <c r="R76" t="n">
-        <v>6907827</v>
+        <v>6908012</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8915,7 +8922,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>naturskogsartad tallskog i blockig östsluttning</t>
+          <t>140-årig blåbärstallskog, med lite granunderväxt</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8937,45 +8944,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>96790516</v>
+        <v>96790504</v>
       </c>
       <c r="B77" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>502213</v>
+        <v>502128</v>
       </c>
       <c r="R77" t="n">
-        <v>6908014</v>
+        <v>6908142</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9021,7 +9028,15 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>150-årig barrblandskog med lågörtsfläckat och asp</t>
+          <t>140-årig barrblandskog i moränsvacka</t>
+        </is>
+      </c>
+      <c r="AN77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>5 substratenheter # grova gamla aspar</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9043,45 +9058,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>96790530</v>
+        <v>96790505</v>
       </c>
       <c r="B78" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>502290</v>
+        <v>501985</v>
       </c>
       <c r="R78" t="n">
-        <v>6907971</v>
+        <v>6908213</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9127,7 +9142,15 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>140-årig blåbärstallskog, med lite granunderväxt och spridda aspar</t>
+          <t>140-årig barrblandskog i blockig svacka</t>
+        </is>
+      </c>
+      <c r="AN78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>2 substratenheter # äldre sälg och asp</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9149,10 +9172,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>96790503</v>
+        <v>96790506</v>
       </c>
       <c r="B79" t="n">
-        <v>79917</v>
+        <v>80432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9160,21 +9183,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9184,10 +9207,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>501952</v>
+        <v>501933</v>
       </c>
       <c r="R79" t="n">
-        <v>6908101</v>
+        <v>6908251</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9233,15 +9256,15 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>140-årig tallskog i nordsida, med brandspår och björk</t>
+          <t>140-årig tallskog med granunderväxt på morän</t>
         </is>
       </c>
       <c r="AN79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov skorstenshögstubbe</t>
+          <t>2 substratenheter # äldre sälgar</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9263,10 +9286,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>96790488</v>
+        <v>96790518</v>
       </c>
       <c r="B80" t="n">
-        <v>93189</v>
+        <v>80432</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9274,43 +9297,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>501832</v>
+        <v>502167</v>
       </c>
       <c r="R80" t="n">
-        <v>6908125</v>
+        <v>6908081</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9356,12 +9370,15 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>140-årig, senvuxen tallskog</t>
-        </is>
+          <t>140-årig mossig blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AN80" t="n">
+        <v>1</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>i stigkant</t>
+          <t>1 substratenheter # äldre klen sälg</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9383,10 +9400,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>96790522</v>
+        <v>96790521</v>
       </c>
       <c r="B81" t="n">
-        <v>89156</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9394,43 +9411,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>502167</v>
+        <v>502153</v>
       </c>
       <c r="R81" t="n">
-        <v>6908110</v>
+        <v>6908101</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9477,6 +9485,14 @@
       <c r="AI81" t="inlineStr">
         <is>
           <t>140-årig blåbärstallskog, med graninslag</t>
+        </is>
+      </c>
+      <c r="AN81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>1 substratenheter # äldre klen sälg</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9498,45 +9514,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>96790504</v>
+        <v>96790516</v>
       </c>
       <c r="B82" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>502128</v>
+        <v>502213</v>
       </c>
       <c r="R82" t="n">
-        <v>6908142</v>
+        <v>6908014</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9582,15 +9598,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>140-årig barrblandskog i moränsvacka</t>
-        </is>
-      </c>
-      <c r="AN82" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>5 substratenheter # grova gamla aspar</t>
+          <t>150-årig barrblandskog med lågörtsfläckat och asp</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9612,45 +9620,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>96790505</v>
+        <v>96790523</v>
       </c>
       <c r="B83" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>501985</v>
+        <v>502175</v>
       </c>
       <c r="R83" t="n">
-        <v>6908213</v>
+        <v>6908132</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9696,15 +9704,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>140-årig barrblandskog i blockig svacka</t>
-        </is>
-      </c>
-      <c r="AN83" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>2 substratenheter # äldre sälg och asp</t>
+          <t>140-årig blåbärstallskog, med graninslag</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9726,45 +9726,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>96790506</v>
+        <v>96790530</v>
       </c>
       <c r="B84" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>501933</v>
+        <v>502290</v>
       </c>
       <c r="R84" t="n">
-        <v>6908251</v>
+        <v>6907971</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9810,15 +9810,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig tallskog med granunderväxt på morän</t>
-        </is>
-      </c>
-      <c r="AN84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>2 substratenheter # äldre sälgar</t>
+          <t>140-årig blåbärstallskog, med lite granunderväxt och spridda aspar</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9840,45 +9832,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>96790523</v>
+        <v>96790503</v>
       </c>
       <c r="B85" t="n">
-        <v>99118</v>
+        <v>79917</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>502175</v>
+        <v>501952</v>
       </c>
       <c r="R85" t="n">
-        <v>6908132</v>
+        <v>6908101</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9924,7 +9916,15 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>140-årig blåbärstallskog, med graninslag</t>
+          <t>140-årig tallskog i nordsida, med brandspår och björk</t>
+        </is>
+      </c>
+      <c r="AN85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10884,7 +10884,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>96790546</v>
+        <v>96790514</v>
       </c>
       <c r="B95" t="n">
         <v>78993</v>
@@ -10915,14 +10915,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502370</v>
+        <v>502414</v>
       </c>
       <c r="R95" t="n">
-        <v>6907089</v>
+        <v>6907420</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10949,12 +10949,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10968,15 +10968,15 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>tallnaturskog med gamla tallöverståndare på blockig mark, ovan sumpskogsparti</t>
+          <t>tallnaturskog i blockig östsluttning</t>
         </is>
       </c>
       <c r="AN95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>2 substratenheter # fallna gamla torrakor</t>
+          <t>1 substratenheter # fallen torraka</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10998,7 +10998,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>96790548</v>
+        <v>96790546</v>
       </c>
       <c r="B96" t="n">
         <v>78993</v>
@@ -11033,10 +11033,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502361</v>
+        <v>502370</v>
       </c>
       <c r="R96" t="n">
-        <v>6907122</v>
+        <v>6907089</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>ogallrad 130-årig lingontallskog med gamla tallöverståndare på blockig mark</t>
+          <t>tallnaturskog med gamla tallöverståndare på blockig mark, ovan sumpskogsparti</t>
         </is>
       </c>
       <c r="AN96" t="n">
@@ -11112,49 +11112,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>111804077</v>
+        <v>96790548</v>
       </c>
       <c r="B97" t="n">
-        <v>93213</v>
+        <v>78993</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Torrflonäsberget, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>502370</v>
+        <v>502361</v>
       </c>
       <c r="R97" t="n">
-        <v>6906961</v>
+        <v>6907122</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11178,22 +11177,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11204,26 +11193,43 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>ogallrad 130-årig lingontallskog med gamla tallöverståndare på blockig mark</t>
+        </is>
+      </c>
+      <c r="AN97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>2 substratenheter # fallna gamla torrakor</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>96790545</v>
+        <v>96790512</v>
       </c>
       <c r="B98" t="n">
-        <v>91962</v>
+        <v>81312</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11231,34 +11237,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lokberget, södra delan, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>502430</v>
+        <v>502354</v>
       </c>
       <c r="R98" t="n">
-        <v>6907162</v>
+        <v>6907377</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11285,12 +11291,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11304,7 +11310,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
+          <t>tallnaturskog på blockig mark</t>
         </is>
       </c>
       <c r="AN98" t="n">
@@ -11312,7 +11318,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga</t>
+          <t>1 substratenheter # torraka</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11334,48 +11340,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>96790514</v>
+        <v>111804077</v>
       </c>
       <c r="B99" t="n">
-        <v>78993</v>
+        <v>93213</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Torrflonäsberget, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>502414</v>
+        <v>502370</v>
       </c>
       <c r="R99" t="n">
-        <v>6907420</v>
+        <v>6906961</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11399,12 +11406,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11415,43 +11432,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>tallnaturskog i blockig östsluttning</t>
-        </is>
-      </c>
-      <c r="AN99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>1 substratenheter # fallen torraka</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>96790512</v>
+        <v>96790545</v>
       </c>
       <c r="B100" t="n">
-        <v>81312</v>
+        <v>91962</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11459,34 +11459,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, södra delan, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>502354</v>
+        <v>502430</v>
       </c>
       <c r="R100" t="n">
-        <v>6907377</v>
+        <v>6907162</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11513,12 +11513,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>tallnaturskog på blockig mark</t>
+          <t>tallnaturskog med gamla tallöverståndare på blockig mark</t>
         </is>
       </c>
       <c r="AN100" t="n">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>1 substratenheter # torraka</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11562,10 +11562,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>96790515</v>
+        <v>96790513</v>
       </c>
       <c r="B101" t="n">
-        <v>80432</v>
+        <v>79085</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11573,34 +11573,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lokberget, öst om, Mpd</t>
+          <t>Lokberget, nordväst om, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>502410</v>
+        <v>502433</v>
       </c>
       <c r="R101" t="n">
-        <v>6907490</v>
+        <v>6907292</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11650,11 +11650,11 @@
         </is>
       </c>
       <c r="AN101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal krumböjd björk</t>
+          <t>5 substratenheter # grova brandhögstubbar</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11676,10 +11676,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>96790513</v>
+        <v>96790535</v>
       </c>
       <c r="B102" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11687,34 +11687,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lokberget, nordväst om, Mpd</t>
+          <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>502433</v>
+        <v>502412</v>
       </c>
       <c r="R102" t="n">
-        <v>6907292</v>
+        <v>6907750</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11760,15 +11760,15 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>tallnaturskog i blockig östsluttning</t>
+          <t>120-årig blockig tallskog nära sjön</t>
         </is>
       </c>
       <c r="AN102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>5 substratenheter # grova brandhögstubbar</t>
+          <t>1 substratenheter # fallen grov gammal torraka</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11790,10 +11790,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>96790535</v>
+        <v>96790533</v>
       </c>
       <c r="B103" t="n">
-        <v>78993</v>
+        <v>89156</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11801,34 +11801,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>4412</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>502412</v>
+        <v>502373</v>
       </c>
       <c r="R103" t="n">
-        <v>6907750</v>
+        <v>6907809</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11874,15 +11883,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>120-årig blockig tallskog nära sjön</t>
-        </is>
-      </c>
-      <c r="AN103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>1 substratenheter # fallen grov gammal torraka</t>
+          <t>140-årig blockig tallskog, med granunderväxt och spridda aspar</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11904,10 +11905,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>96790533</v>
+        <v>96790515</v>
       </c>
       <c r="B104" t="n">
-        <v>89156</v>
+        <v>80432</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11915,43 +11916,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Lokberget, öst om, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>502373</v>
+        <v>502410</v>
       </c>
       <c r="R104" t="n">
-        <v>6907809</v>
+        <v>6907490</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11997,7 +11989,15 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>140-årig blockig tallskog, med granunderväxt och spridda aspar</t>
+          <t>tallnaturskog i blockig östsluttning</t>
+        </is>
+      </c>
+      <c r="AN104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal krumböjd björk</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12247,10 +12247,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134958086</v>
+        <v>134968660</v>
       </c>
       <c r="B107" t="n">
-        <v>91974</v>
+        <v>79039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12258,21 +12258,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12282,10 +12282,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503072</v>
+        <v>503205</v>
       </c>
       <c r="R107" t="n">
-        <v>6905853</v>
+        <v>6906127</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12344,10 +12344,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134970483</v>
+        <v>134958086</v>
       </c>
       <c r="B108" t="n">
-        <v>79131</v>
+        <v>91974</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12355,21 +12355,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503042</v>
+        <v>503072</v>
       </c>
       <c r="R108" t="n">
-        <v>6905794</v>
+        <v>6905853</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12441,10 +12441,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134966338</v>
+        <v>134958497</v>
       </c>
       <c r="B109" t="n">
-        <v>79963</v>
+        <v>93271</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12452,21 +12452,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12476,10 +12476,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503042</v>
+        <v>503146</v>
       </c>
       <c r="R109" t="n">
-        <v>6905796</v>
+        <v>6906009</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12538,32 +12538,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134968660</v>
+        <v>134960676</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>79397</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12573,10 +12573,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503205</v>
+        <v>503129</v>
       </c>
       <c r="R110" t="n">
-        <v>6906127</v>
+        <v>6905997</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12635,32 +12635,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134958497</v>
+        <v>134966756</v>
       </c>
       <c r="B111" t="n">
-        <v>93271</v>
+        <v>79397</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12670,10 +12670,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>503146</v>
+        <v>503131</v>
       </c>
       <c r="R111" t="n">
-        <v>6906009</v>
+        <v>6906076</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12732,7 +12732,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134960676</v>
+        <v>134970054</v>
       </c>
       <c r="B112" t="n">
         <v>79397</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>503129</v>
+        <v>503060</v>
       </c>
       <c r="R112" t="n">
-        <v>6905997</v>
+        <v>6905865</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12829,32 +12829,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134966756</v>
+        <v>134963939</v>
       </c>
       <c r="B113" t="n">
-        <v>79397</v>
+        <v>78776</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>503131</v>
+        <v>503142</v>
       </c>
       <c r="R113" t="n">
-        <v>6906076</v>
+        <v>6906039</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12926,32 +12926,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134970054</v>
+        <v>134959531</v>
       </c>
       <c r="B114" t="n">
-        <v>79397</v>
+        <v>79130</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12961,10 +12961,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>503060</v>
+        <v>503138</v>
       </c>
       <c r="R114" t="n">
-        <v>6905865</v>
+        <v>6906322</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13023,10 +13023,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134963939</v>
+        <v>134961562</v>
       </c>
       <c r="B115" t="n">
-        <v>78776</v>
+        <v>79130</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13034,21 +13034,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13058,10 +13058,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>503142</v>
+        <v>503195</v>
       </c>
       <c r="R115" t="n">
-        <v>6906039</v>
+        <v>6906171</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13120,10 +13120,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134961562</v>
+        <v>134961997</v>
       </c>
       <c r="B116" t="n">
-        <v>79130</v>
+        <v>79992</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13131,21 +13131,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13155,10 +13155,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>503195</v>
+        <v>503137</v>
       </c>
       <c r="R116" t="n">
-        <v>6906171</v>
+        <v>6906035</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13217,7 +13217,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134961997</v>
+        <v>134964561</v>
       </c>
       <c r="B117" t="n">
         <v>79992</v>
@@ -13252,10 +13252,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>503137</v>
+        <v>503215</v>
       </c>
       <c r="R117" t="n">
-        <v>6906035</v>
+        <v>6906123</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13314,7 +13314,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134964561</v>
+        <v>134966337</v>
       </c>
       <c r="B118" t="n">
         <v>79992</v>
@@ -13349,10 +13349,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>503215</v>
+        <v>503139</v>
       </c>
       <c r="R118" t="n">
-        <v>6906123</v>
+        <v>6906002</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13411,7 +13411,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134966337</v>
+        <v>134970053</v>
       </c>
       <c r="B119" t="n">
         <v>79992</v>
@@ -13446,10 +13446,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>503139</v>
+        <v>503193</v>
       </c>
       <c r="R119" t="n">
-        <v>6906002</v>
+        <v>6906126</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13508,10 +13508,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134970053</v>
+        <v>134968039</v>
       </c>
       <c r="B120" t="n">
-        <v>79992</v>
+        <v>78377</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13519,21 +13519,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13543,10 +13543,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>503193</v>
+        <v>503172</v>
       </c>
       <c r="R120" t="n">
-        <v>6906126</v>
+        <v>6906090</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13605,7 +13605,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134968039</v>
+        <v>134968447</v>
       </c>
       <c r="B121" t="n">
         <v>78377</v>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>503172</v>
+        <v>503142</v>
       </c>
       <c r="R121" t="n">
-        <v>6906090</v>
+        <v>6906039</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134968447</v>
+        <v>134968867</v>
       </c>
       <c r="B122" t="n">
         <v>78377</v>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>503142</v>
+        <v>503193</v>
       </c>
       <c r="R122" t="n">
-        <v>6906039</v>
+        <v>6906172</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134968867</v>
+        <v>134956702</v>
       </c>
       <c r="B123" t="n">
-        <v>78377</v>
+        <v>79131</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13810,21 +13810,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13834,10 +13834,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>503193</v>
+        <v>503142</v>
       </c>
       <c r="R123" t="n">
-        <v>6906172</v>
+        <v>6906041</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13896,7 +13896,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134956702</v>
+        <v>134958500</v>
       </c>
       <c r="B124" t="n">
         <v>79131</v>
@@ -13931,10 +13931,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>503142</v>
+        <v>503137</v>
       </c>
       <c r="R124" t="n">
-        <v>6906041</v>
+        <v>6906035</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13993,7 +13993,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134958500</v>
+        <v>134958720</v>
       </c>
       <c r="B125" t="n">
         <v>79131</v>
@@ -14028,10 +14028,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>503137</v>
+        <v>503111</v>
       </c>
       <c r="R125" t="n">
-        <v>6906035</v>
+        <v>6906007</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14090,7 +14090,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134958720</v>
+        <v>134962693</v>
       </c>
       <c r="B126" t="n">
         <v>79131</v>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>503111</v>
+        <v>503216</v>
       </c>
       <c r="R126" t="n">
-        <v>6906007</v>
+        <v>6906119</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14187,7 +14187,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134962693</v>
+        <v>134965491</v>
       </c>
       <c r="B127" t="n">
         <v>79131</v>
@@ -14222,10 +14222,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>503216</v>
+        <v>503137</v>
       </c>
       <c r="R127" t="n">
-        <v>6906119</v>
+        <v>6906324</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14478,10 +14478,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134955926</v>
+        <v>134970483</v>
       </c>
       <c r="B130" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14489,21 +14489,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14513,10 +14513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>503131</v>
+        <v>503042</v>
       </c>
       <c r="R130" t="n">
-        <v>6906105</v>
+        <v>6905794</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14575,7 +14575,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134967185</v>
+        <v>134955926</v>
       </c>
       <c r="B131" t="n">
         <v>79963</v>
@@ -14610,10 +14610,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>503191</v>
+        <v>503131</v>
       </c>
       <c r="R131" t="n">
-        <v>6906087</v>
+        <v>6906105</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14672,7 +14672,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134967807</v>
+        <v>134966338</v>
       </c>
       <c r="B132" t="n">
         <v>79963</v>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>503139</v>
+        <v>503042</v>
       </c>
       <c r="R132" t="n">
-        <v>6906009</v>
+        <v>6905796</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14769,7 +14769,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134968042</v>
+        <v>134967185</v>
       </c>
       <c r="B133" t="n">
         <v>79963</v>
@@ -14804,10 +14804,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>503120</v>
+        <v>503191</v>
       </c>
       <c r="R133" t="n">
-        <v>6906078</v>
+        <v>6906087</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14866,7 +14866,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134970482</v>
+        <v>134967807</v>
       </c>
       <c r="B134" t="n">
         <v>79963</v>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>503143</v>
+        <v>503139</v>
       </c>
       <c r="R134" t="n">
-        <v>6906039</v>
+        <v>6906009</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14963,10 +14963,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134959129</v>
+        <v>134968042</v>
       </c>
       <c r="B135" t="n">
-        <v>79039</v>
+        <v>79963</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14974,21 +14974,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>503123</v>
+        <v>503120</v>
       </c>
       <c r="R135" t="n">
-        <v>6906347</v>
+        <v>6906078</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15060,10 +15060,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134967808</v>
+        <v>134970482</v>
       </c>
       <c r="B136" t="n">
-        <v>93271</v>
+        <v>79963</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15071,21 +15071,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>503116</v>
+        <v>503143</v>
       </c>
       <c r="R136" t="n">
-        <v>6906339</v>
+        <v>6906039</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15157,10 +15157,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134959531</v>
+        <v>134959129</v>
       </c>
       <c r="B137" t="n">
-        <v>79130</v>
+        <v>79039</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15168,21 +15168,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>503138</v>
+        <v>503123</v>
       </c>
       <c r="R137" t="n">
-        <v>6906322</v>
+        <v>6906347</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15254,10 +15254,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134963938</v>
+        <v>134967808</v>
       </c>
       <c r="B138" t="n">
-        <v>78377</v>
+        <v>93271</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15265,21 +15265,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>503145</v>
+        <v>503116</v>
       </c>
       <c r="R138" t="n">
-        <v>6906340</v>
+        <v>6906339</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15351,10 +15351,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>134965491</v>
+        <v>134963938</v>
       </c>
       <c r="B139" t="n">
-        <v>79131</v>
+        <v>78377</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15362,21 +15362,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15386,10 +15386,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>503137</v>
+        <v>503145</v>
       </c>
       <c r="R139" t="n">
-        <v>6906324</v>
+        <v>6906340</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
